--- a/data/trans_orig/P25C$parches_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P25C$parches_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según método de dejar de fumar (multirrespuesta) en 2023</t>
+          <t>Población según método de dejar de fumar (multirrespuesta) en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22890</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19343</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25408</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>36128</t>
+          <t>37507</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>48960</t>
+          <t>49712</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31787</t>
+          <t>31362</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43297</t>
+          <t>42939</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42921</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50324</t>
+          <t>50136</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78254</t>
+          <t>77811</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91658</t>
+          <t>91586</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>841</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>313694</t>
+          <t>314087</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>347127</t>
+          <t>346703</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>73793</t>
+          <t>74370</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82491</t>
+          <t>82680</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>391343</t>
+          <t>393244</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>429979</t>
+          <t>431172</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17587</t>
+          <t>18018</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>830</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>559</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>123697</t>
+          <t>122491</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>140827</t>
+          <t>140257</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>68036</t>
+          <t>68685</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>78289</t>
+          <t>78541</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>195665</t>
+          <t>195753</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>215708</t>
+          <t>216133</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>15807</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>485</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17542</t>
+          <t>17617</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4588,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>17827</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4623,12 +4623,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22319</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>570</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>134505</t>
+          <t>134232</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>146796</t>
+          <t>146319</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>36177</t>
+          <t>36115</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>42721</t>
+          <t>42666</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>172725</t>
+          <t>172871</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>186839</t>
+          <t>187233</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>583</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>105611</t>
+          <t>105829</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>113698</t>
+          <t>113638</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>17120</t>
+          <t>17217</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>121956</t>
+          <t>121795</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>130279</t>
+          <t>130168</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>15018</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>28718</t>
+          <t>28695</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9829</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>834</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>753362</t>
+          <t>753183</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>824064</t>
+          <t>824349</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>294702</t>
+          <t>294116</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>311951</t>
+          <t>311532</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1058013</t>
+          <t>1056936</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>1138617</t>
+          <t>1136007</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>40205</t>
+          <t>38177</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>16891</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>49324</t>
+          <t>49429</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>39834</t>
+          <t>40995</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>17537</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>48026</t>
+          <t>49645</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C$parches_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P25C$parches_2023-Edad-trans_orig.xlsx
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>37,84%</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>20336</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>24432</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,27 +2007,27 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29449</t>
+          <t>32988</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24467</t>
+          <t>27553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>34069</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>45040</t>
+          <t>53323</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37507</t>
+          <t>44548</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>49712</t>
+          <t>58175</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>661</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>755</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>755</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>39103</t>
+          <t>43050</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31362</t>
+          <t>35041</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42939</t>
+          <t>46960</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>47441</t>
+          <t>51312</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>46534</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50136</t>
+          <t>54370</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>86544</t>
+          <t>94362</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77811</t>
+          <t>85810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91586</t>
+          <t>100078</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12529</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>710</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>338870</t>
+          <t>103920</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>314087</t>
+          <t>95720</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>346703</t>
+          <t>109172</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>79198</t>
+          <t>83891</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74370</t>
+          <t>78599</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82680</t>
+          <t>87848</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>418068</t>
+          <t>187811</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>393244</t>
+          <t>177663</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>431172</t>
+          <t>194350</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18018</t>
+          <t>9430</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -3788,32 +3788,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2463</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4028,12 +4028,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>590</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -4098,12 +4098,12 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>132856</t>
+          <t>139599</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>122491</t>
+          <t>129871</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>140257</t>
+          <t>147733</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>74026</t>
+          <t>81364</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>68685</t>
+          <t>75507</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>78541</t>
+          <t>86202</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>206882</t>
+          <t>220963</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>195753</t>
+          <t>209790</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>216133</t>
+          <t>230143</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>15807</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>523</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17617</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -4583,32 +4583,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>17827</t>
+          <t>18922</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4618,22 +4618,22 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>13594</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>22319</t>
+          <t>23156</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>587</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>669</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>141129</t>
+          <t>155344</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>134232</t>
+          <t>147271</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>146319</t>
+          <t>161090</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>40008</t>
+          <t>42749</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>36115</t>
+          <t>38220</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>42666</t>
+          <t>45546</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>181138</t>
+          <t>198093</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>172871</t>
+          <t>188861</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>187233</t>
+          <t>204298</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -5265,102 +5265,102 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>8165</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3719</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>4886</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2112</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>10135</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
           <t>2,22%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>997</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>3598</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>4450</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>9166</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -5378,32 +5378,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>610</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5448,32 +5448,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7909</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>504</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5731,12 +5731,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>646</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,22 +5904,22 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>110827</t>
+          <t>121940</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>105829</t>
+          <t>116390</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>113638</t>
+          <t>125622</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>17617</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>14704</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>17217</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>126601</t>
+          <t>139558</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>121795</t>
+          <t>133641</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>130168</t>
+          <t>143576</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>908</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>868</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>430</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>670</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6243,32 +6243,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -6290,32 +6290,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,32 +6325,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>28695</t>
+          <t>28574</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6403,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6438,32 +6438,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>17349</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,22 +6586,22 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,27 +6664,27 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>786038</t>
+          <t>590654</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>753183</t>
+          <t>571253</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>824349</t>
+          <t>605462</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>330202</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>294116</t>
+          <t>320890</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>311532</t>
+          <t>339402</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>1090232</t>
+          <t>920856</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1056936</t>
+          <t>901378</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>1136007</t>
+          <t>938614</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>15407</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>36890</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>17238</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>50963</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -6968,32 +6968,32 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>40995</t>
+          <t>40558</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7003,32 +7003,32 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>15108</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7038,32 +7038,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>37593</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>27280</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>49645</t>
+          <t>50816</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
